--- a/InputData/trans/BLP/BAU LCFS Perc.xlsx
+++ b/InputData/trans/BLP/BAU LCFS Perc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\VA\trans\BLP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/VA/trans/BLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98DB8E0F-27B5-4008-9565-18D68042EE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F10AAA6-FE9F-DA4E-BAFB-78E7E516E18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1110" windowWidth="13035" windowHeight="16890" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="400" yWindow="760" windowWidth="13040" windowHeight="16900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -932,13 +931,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="56.7109375" customWidth="1"/>
+    <col min="2" max="2" width="56.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,7 +945,7 @@
         <v>103</v>
       </c>
       <c r="C1" s="9">
-        <v>45258</v>
+        <v>45296</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>13</v>
@@ -955,7 +954,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
         <f>LOOKUP(B1,E2:F51,F2:F51)</f>
         <v>VA</v>
@@ -967,7 +966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -981,7 +980,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>7</v>
@@ -993,7 +992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
@@ -1004,7 +1003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -1015,7 +1014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +1025,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E8" s="8" t="s">
         <v>25</v>
       </c>
@@ -1034,7 +1033,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E9" s="8" t="s">
         <v>27</v>
       </c>
@@ -1042,7 +1041,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1053,7 +1052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E11" s="8" t="s">
         <v>31</v>
       </c>
@@ -1061,7 +1060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -1069,7 +1068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E13" s="8" t="s">
         <v>35</v>
       </c>
@@ -1077,7 +1076,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E14" s="8" t="s">
         <v>37</v>
       </c>
@@ -1085,7 +1084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E15" s="8" t="s">
         <v>39</v>
       </c>
@@ -1093,7 +1092,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E16" s="8" t="s">
         <v>41</v>
       </c>
@@ -1101,7 +1100,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E17" s="8" t="s">
         <v>43</v>
       </c>
@@ -1109,7 +1108,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E18" s="8" t="s">
         <v>45</v>
       </c>
@@ -1117,7 +1116,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E19" s="8" t="s">
         <v>47</v>
       </c>
@@ -1125,7 +1124,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E20" s="8" t="s">
         <v>49</v>
       </c>
@@ -1133,7 +1132,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E21" s="8" t="s">
         <v>51</v>
       </c>
@@ -1141,7 +1140,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E22" s="8" t="s">
         <v>53</v>
       </c>
@@ -1149,7 +1148,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E23" s="8" t="s">
         <v>55</v>
       </c>
@@ -1157,7 +1156,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E24" s="8" t="s">
         <v>57</v>
       </c>
@@ -1165,7 +1164,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -1187,7 +1186,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -1198,7 +1197,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1210,7 +1209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E28" s="8" t="s">
         <v>65</v>
       </c>
@@ -1218,7 +1217,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E29" s="8" t="s">
         <v>67</v>
       </c>
@@ -1226,7 +1225,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E30" s="8" t="s">
         <v>69</v>
       </c>
@@ -1234,7 +1233,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E31" s="8" t="s">
         <v>71</v>
       </c>
@@ -1242,7 +1241,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E32" s="8" t="s">
         <v>73</v>
       </c>
@@ -1250,7 +1249,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E33" s="8" t="s">
         <v>75</v>
       </c>
@@ -1258,7 +1257,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E34" s="8" t="s">
         <v>77</v>
       </c>
@@ -1266,7 +1265,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E35" s="8" t="s">
         <v>79</v>
       </c>
@@ -1274,7 +1273,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E36" s="8" t="s">
         <v>81</v>
       </c>
@@ -1282,7 +1281,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E37" s="8" t="s">
         <v>83</v>
       </c>
@@ -1290,7 +1289,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E38" s="8" t="s">
         <v>85</v>
       </c>
@@ -1298,7 +1297,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E39" s="8" t="s">
         <v>87</v>
       </c>
@@ -1306,7 +1305,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E40" s="8" t="s">
         <v>89</v>
       </c>
@@ -1314,7 +1313,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E41" s="8" t="s">
         <v>91</v>
       </c>
@@ -1322,7 +1321,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E42" s="8" t="s">
         <v>93</v>
       </c>
@@ -1330,7 +1329,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E43" s="8" t="s">
         <v>95</v>
       </c>
@@ -1338,7 +1337,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E44" s="8" t="s">
         <v>97</v>
       </c>
@@ -1346,7 +1345,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E45" s="8" t="s">
         <v>99</v>
       </c>
@@ -1354,7 +1353,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E46" s="8" t="s">
         <v>101</v>
       </c>
@@ -1362,7 +1361,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E47" s="8" t="s">
         <v>103</v>
       </c>
@@ -1370,7 +1369,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E48" s="8" t="s">
         <v>105</v>
       </c>
@@ -1378,7 +1377,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E49" s="8" t="s">
         <v>107</v>
       </c>
@@ -1386,7 +1385,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E50" s="8" t="s">
         <v>109</v>
       </c>
@@ -1394,7 +1393,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E51" s="8" t="s">
         <v>111</v>
       </c>
@@ -1414,14 +1413,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C345DB-5104-4418-B999-526D8ADFEBDA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1449,12 +1448,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B1">
         <v>2018</v>
       </c>
@@ -1555,7 +1554,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1692,14 +1691,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
